--- a/output/pdf_financials_xlsx/LQWD.xlsx
+++ b/output/pdf_financials_xlsx/LQWD.xlsx
@@ -4530,10 +4530,10 @@
         <v>2.747746</v>
       </c>
       <c r="L91" s="3" t="n">
-        <v>7.511581</v>
+        <v>4.763835</v>
       </c>
       <c r="M91" s="3" t="n">
-        <v>0</v>
+        <v>-7.511581</v>
       </c>
     </row>
     <row r="92">
@@ -5651,13 +5651,13 @@
         </is>
       </c>
       <c r="B118" s="3" t="n">
-        <v>0.148723</v>
+        <v>-0.417963</v>
       </c>
       <c r="C118" s="3" t="n">
-        <v>0.001253</v>
+        <v>-0.288026</v>
       </c>
       <c r="D118" s="3" t="n">
-        <v>0</v>
+        <v>-0.15713</v>
       </c>
       <c r="E118" s="3" t="n">
         <v>0</v>
@@ -9000,7 +9000,11 @@
           <t>Change in revaluation reserve (Note 7)</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E35" t="inlineStr">
         <is>
           <t>-</t>
@@ -24736,7 +24740,11 @@
           <t>Exploration and evaluation asset expenditures</t>
         </is>
       </c>
-      <c r="D246" t="inlineStr"/>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E246" t="inlineStr">
         <is>
           <t>-</t>
@@ -25644,7 +25652,11 @@
           <t>Exploration and evaluation asset expenditures</t>
         </is>
       </c>
-      <c r="D258" t="inlineStr"/>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E258" s="5" t="n">
         <v>-0.566686</v>
       </c>

--- a/output/pdf_financials_xlsx/LQWD.xlsx
+++ b/output/pdf_financials_xlsx/LQWD.xlsx
@@ -895,13 +895,13 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.059802</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.014174</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.015925</v>
       </c>
       <c r="E12" s="3" t="n">
         <v>0</v>
@@ -1624,13 +1624,13 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-1.447967</v>
+        <v>-1.507769</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-7.608233</v>
+        <v>-7.622407</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-5.442967</v>
+        <v>-5.458892</v>
       </c>
       <c r="E27" s="3" t="n">
         <v>-0.090679</v>
@@ -1714,13 +1714,13 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-1.447967</v>
+        <v>-1.507769</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-7.608233</v>
+        <v>-7.622407</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-5.442967</v>
+        <v>-5.458892</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>-0.090679</v>
@@ -38592,7 +38592,7 @@
       </c>
       <c r="D430" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E430" s="5" t="n">

--- a/output/pdf_financials_xlsx/LQWD.xlsx
+++ b/output/pdf_financials_xlsx/LQWD.xlsx
@@ -4892,22 +4892,22 @@
         <v>0</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>0</v>
+        <v>0.100021</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>0</v>
+        <v>0.178556</v>
       </c>
       <c r="I100" s="3" t="n">
-        <v>0</v>
+        <v>0.827291</v>
       </c>
       <c r="J100" s="3" t="n">
-        <v>0</v>
+        <v>1.031858</v>
       </c>
       <c r="K100" s="3" t="n">
-        <v>0</v>
+        <v>1.023762</v>
       </c>
       <c r="L100" s="3" t="n">
-        <v>0</v>
+        <v>0.174263</v>
       </c>
       <c r="M100" s="3" t="n">
         <v>0</v>
@@ -16770,7 +16770,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -18774,7 +18774,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -21442,7 +21442,11 @@
           <t>Additions to intangible assets</t>
         </is>
       </c>
-      <c r="D202" t="inlineStr"/>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E202" t="inlineStr">
         <is>
           <t>-</t>
@@ -26186,7 +26190,7 @@
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
@@ -29482,7 +29486,7 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">

--- a/output/pdf_financials_xlsx/LQWD.xlsx
+++ b/output/pdf_financials_xlsx/LQWD.xlsx
@@ -670,22 +670,22 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.775147</v>
+        <v>0.846287</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.288401</v>
+        <v>0.328151</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.102811</v>
+        <v>0.131061</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.065788</v>
+        <v>0.066788</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.045406</v>
+        <v>0.046656</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.079012</v>
+        <v>0.080262</v>
       </c>
       <c r="H7" s="3" t="n">
         <v>0.007703</v>
@@ -811,16 +811,16 @@
         <v>0.62931</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.146683</v>
+        <v>0.174933</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.072642</v>
+        <v>0.073642</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.145395</v>
+        <v>0.146645</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.464235</v>
+        <v>0.465485</v>
       </c>
       <c r="H10" s="3" t="n">
         <v>0.270612</v>
@@ -856,16 +856,16 @@
         <v>-0.62931</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>-0.146683</v>
+        <v>-0.174933</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>-0.072642</v>
+        <v>-0.073642</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>-0.145395</v>
+        <v>-0.146645</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>-0.411604</v>
+        <v>-0.412854</v>
       </c>
       <c r="H11" s="3" t="n">
         <v>-0.144493</v>
@@ -1299,10 +1299,10 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>-1.447967</v>
+        <v>-0.991054</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>-7.608233</v>
+        <v>-0.980191</v>
       </c>
       <c r="D20" s="3" t="n">
         <v>-5.442967</v>
@@ -1344,10 +1344,10 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>0</v>
+        <v>-0.456913</v>
       </c>
       <c r="C21" s="3" t="n">
-        <v>0</v>
+        <v>-6.628042</v>
       </c>
       <c r="D21" s="3" t="n">
         <v>0</v>
@@ -5531,10 +5531,10 @@
         <v>0</v>
       </c>
       <c r="E115" s="3" t="n">
-        <v>0</v>
+        <v>0.08333</v>
       </c>
       <c r="F115" s="3" t="n">
-        <v>0</v>
+        <v>0.08008</v>
       </c>
       <c r="G115" s="3" t="n">
         <v>0</v>
@@ -21290,7 +21290,11 @@
           <t>Cash received by private placement</t>
         </is>
       </c>
-      <c r="D200" t="inlineStr"/>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E200" t="inlineStr">
         <is>
           <t>-</t>
@@ -22806,7 +22810,11 @@
           <t>Proceeds on sale of marketable securities</t>
         </is>
       </c>
-      <c r="D220" t="inlineStr"/>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E220" t="inlineStr">
         <is>
           <t>-</t>
@@ -33006,7 +33014,11 @@
           <t>Director fees</t>
         </is>
       </c>
-      <c r="D356" t="inlineStr"/>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E356" t="inlineStr">
         <is>
           <t>-</t>
@@ -34674,7 +34686,11 @@
           <t>Director fees</t>
         </is>
       </c>
-      <c r="D378" t="inlineStr"/>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E378" t="inlineStr">
         <is>
           <t>-</t>
@@ -35738,7 +35754,11 @@
           <t>Consulting and director fees</t>
         </is>
       </c>
-      <c r="D392" t="inlineStr"/>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E392" s="5" t="n">
         <v>0.07113999999999999</v>
       </c>
@@ -36932,7 +36952,11 @@
           <t>Consulting and director fees</t>
         </is>
       </c>
-      <c r="D408" t="inlineStr"/>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E408" t="inlineStr">
         <is>
           <t>-</t>
@@ -38818,7 +38842,11 @@
           <t>Net loss from continuing operations</t>
         </is>
       </c>
-      <c r="D433" t="inlineStr"/>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>NetIncomeContinuousOperations</t>
+        </is>
+      </c>
       <c r="E433" t="inlineStr">
         <is>
           <t>-</t>
@@ -39272,7 +39300,11 @@
           <t>Net loss from continuing operations</t>
         </is>
       </c>
-      <c r="D439" t="inlineStr"/>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>NetIncomeContinuousOperations</t>
+        </is>
+      </c>
       <c r="E439" s="5" t="n">
         <v>-0.991054</v>
       </c>
@@ -39346,7 +39378,11 @@
           <t>Net loss from discontinued operations (Note 10(a))</t>
         </is>
       </c>
-      <c r="D440" t="inlineStr"/>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E440" s="5" t="n">
         <v>-0.456913</v>
       </c>
